--- a/Data/EXCEL/Transfer/salemon/202512/7791-salemon-202512.xlsx
+++ b/Data/EXCEL/Transfer/salemon/202512/7791-salemon-202512.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\202512\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\WORKSPACES\xls2xlsx\Transfer\202512\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{707CE0FB-B303-419B-9379-9C7FBA2DAEA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{A86F0738-A5A5-449F-A17B-A8E6F3C5B3FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8340" yWindow="930" windowWidth="26910" windowHeight="18975" xr2:uid="{3A919345-530E-4EB1-BFDD-7D9BD07CF633}"/>
+    <workbookView xWindow="0" yWindow="1740" windowWidth="17565" windowHeight="11295" xr2:uid="{93D22BBF-3279-4176-BD91-750249A7351B}"/>
   </bookViews>
   <sheets>
     <sheet name="7791-salemon-202512" sheetId="2" r:id="rId1"/>
@@ -854,16 +854,16 @@
     <xf numFmtId="0" fontId="18" fillId="34" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="34" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="34" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="34" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="34" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="33" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="33" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="34" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1258,18 +1258,18 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CC582313-BE34-4B2F-A926-5143D17A9CCF}">
-  <dimension ref="A1:Q17"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B2E5519-BA6B-495C-B490-FDB08FCA95E0}">
+  <dimension ref="A1:Q18"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.25" customWidth="1"/>
-    <col min="2" max="6" width="12.125" customWidth="1"/>
-    <col min="7" max="7" width="12.75" customWidth="1"/>
-    <col min="8" max="10" width="12.125" customWidth="1"/>
-    <col min="11" max="11" width="12.75" customWidth="1"/>
-    <col min="12" max="15" width="12.125" customWidth="1"/>
-    <col min="16" max="16" width="12.75" customWidth="1"/>
-    <col min="17" max="17" width="14" customWidth="1"/>
+    <col min="1" max="1" width="9.375" customWidth="1"/>
+    <col min="2" max="6" width="7.5" customWidth="1"/>
+    <col min="7" max="7" width="7.875" customWidth="1"/>
+    <col min="8" max="10" width="7.5" customWidth="1"/>
+    <col min="11" max="11" width="7.875" customWidth="1"/>
+    <col min="12" max="15" width="7.5" customWidth="1"/>
+    <col min="16" max="16" width="7.875" customWidth="1"/>
+    <col min="17" max="17" width="9" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:17" x14ac:dyDescent="0.25">
@@ -1422,166 +1422,166 @@
     </row>
     <row r="5" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="5">
-        <v>45962</v>
+        <v>45992</v>
       </c>
       <c r="B5" s="6">
-        <v>81</v>
+        <v>73.599999999999994</v>
       </c>
       <c r="C5" s="6">
-        <v>74</v>
+        <v>72.7</v>
       </c>
       <c r="D5" s="6">
-        <v>81.3</v>
+        <v>74.3</v>
       </c>
       <c r="E5" s="6">
         <v>71</v>
       </c>
       <c r="F5" s="7">
-        <v>-6.9</v>
+        <v>-1.3</v>
       </c>
       <c r="G5" s="7">
-        <v>-8.5299999999999994</v>
+        <v>-1.76</v>
       </c>
       <c r="H5" s="8">
-        <v>1.61</v>
+        <v>1.49</v>
       </c>
       <c r="I5" s="7">
-        <v>-18.7</v>
+        <v>-7.65</v>
       </c>
       <c r="J5" s="7">
-        <v>-9.0299999999999994</v>
+        <v>-7.42</v>
       </c>
       <c r="K5" s="8">
-        <v>24.29</v>
+        <v>25.78</v>
       </c>
       <c r="L5" s="7">
-        <v>-3.13</v>
+        <v>-3.38</v>
       </c>
       <c r="M5" s="8">
-        <v>1.61</v>
+        <v>1.49</v>
       </c>
       <c r="N5" s="7">
-        <v>-18.7</v>
+        <v>-7.65</v>
       </c>
       <c r="O5" s="7">
-        <v>-9.0299999999999994</v>
+        <v>-7.42</v>
       </c>
       <c r="P5" s="8">
-        <v>24.29</v>
+        <v>25.78</v>
       </c>
       <c r="Q5" s="7">
-        <v>-3.13</v>
+        <v>-3.38</v>
       </c>
     </row>
     <row r="6" spans="1:17" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="10">
-        <v>45931</v>
+        <v>45962</v>
       </c>
       <c r="B6" s="11">
-        <v>83.4</v>
+        <v>81</v>
       </c>
       <c r="C6" s="11">
-        <v>80.900000000000006</v>
+        <v>74</v>
       </c>
       <c r="D6" s="11">
-        <v>84.5</v>
+        <v>81.3</v>
       </c>
       <c r="E6" s="11">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="F6" s="12">
-        <v>8.9</v>
+        <v>-6.9</v>
       </c>
       <c r="G6" s="12">
-        <v>12.36</v>
+        <v>-8.5299999999999994</v>
       </c>
       <c r="H6" s="13">
-        <v>1.98</v>
-      </c>
-      <c r="I6" s="14">
-        <v>-17.3</v>
+        <v>1.61</v>
+      </c>
+      <c r="I6" s="12">
+        <v>-18.7</v>
       </c>
       <c r="J6" s="12">
-        <v>3.74</v>
+        <v>-9.0299999999999994</v>
       </c>
       <c r="K6" s="13">
-        <v>22.68</v>
-      </c>
-      <c r="L6" s="14">
-        <v>-2.68</v>
+        <v>24.29</v>
+      </c>
+      <c r="L6" s="12">
+        <v>-3.13</v>
       </c>
       <c r="M6" s="13">
-        <v>1.98</v>
-      </c>
-      <c r="N6" s="14">
-        <v>-17.3</v>
+        <v>1.61</v>
+      </c>
+      <c r="N6" s="12">
+        <v>-18.7</v>
       </c>
       <c r="O6" s="12">
-        <v>3.74</v>
+        <v>-9.0299999999999994</v>
       </c>
       <c r="P6" s="13">
-        <v>22.68</v>
-      </c>
-      <c r="Q6" s="14">
-        <v>-2.68</v>
+        <v>24.29</v>
+      </c>
+      <c r="Q6" s="12">
+        <v>-3.13</v>
       </c>
     </row>
     <row r="7" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="5">
-        <v>45901</v>
-      </c>
-      <c r="B7" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="C7" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="D7" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="E7" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="F7" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="G7" s="8" t="s">
-        <v>17</v>
+        <v>45931</v>
+      </c>
+      <c r="B7" s="6">
+        <v>83.4</v>
+      </c>
+      <c r="C7" s="6">
+        <v>80.900000000000006</v>
+      </c>
+      <c r="D7" s="6">
+        <v>84.5</v>
+      </c>
+      <c r="E7" s="6">
+        <v>80</v>
+      </c>
+      <c r="F7" s="14">
+        <v>8.9</v>
+      </c>
+      <c r="G7" s="14">
+        <v>12.36</v>
       </c>
       <c r="H7" s="8">
-        <v>2.39</v>
+        <v>1.98</v>
       </c>
       <c r="I7" s="7">
-        <v>-16.899999999999999</v>
-      </c>
-      <c r="J7" s="15">
-        <v>2.72</v>
+        <v>-17.3</v>
+      </c>
+      <c r="J7" s="14">
+        <v>3.74</v>
       </c>
       <c r="K7" s="8">
-        <v>20.7</v>
+        <v>22.68</v>
       </c>
       <c r="L7" s="7">
-        <v>-3.25</v>
+        <v>-2.68</v>
       </c>
       <c r="M7" s="8">
-        <v>2.39</v>
+        <v>1.98</v>
       </c>
       <c r="N7" s="7">
-        <v>-16.899999999999999</v>
-      </c>
-      <c r="O7" s="15">
-        <v>2.72</v>
+        <v>-17.3</v>
+      </c>
+      <c r="O7" s="14">
+        <v>3.74</v>
       </c>
       <c r="P7" s="8">
-        <v>20.7</v>
+        <v>22.68</v>
       </c>
       <c r="Q7" s="7">
-        <v>-3.25</v>
+        <v>-2.68</v>
       </c>
     </row>
     <row r="8" spans="1:17" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="10">
-        <v>45870</v>
+        <v>45901</v>
       </c>
       <c r="B8" s="11" t="s">
         <v>17</v>
@@ -1602,39 +1602,39 @@
         <v>17</v>
       </c>
       <c r="H8" s="13">
-        <v>2.88</v>
+        <v>2.39</v>
       </c>
       <c r="I8" s="12">
-        <v>4.8600000000000003</v>
-      </c>
-      <c r="J8" s="14">
-        <v>-1.67</v>
+        <v>-16.899999999999999</v>
+      </c>
+      <c r="J8" s="15">
+        <v>2.72</v>
       </c>
       <c r="K8" s="13">
-        <v>18.309999999999999</v>
-      </c>
-      <c r="L8" s="14">
-        <v>-3.98</v>
+        <v>20.7</v>
+      </c>
+      <c r="L8" s="12">
+        <v>-3.25</v>
       </c>
       <c r="M8" s="13">
-        <v>2.88</v>
+        <v>2.39</v>
       </c>
       <c r="N8" s="12">
-        <v>4.8600000000000003</v>
-      </c>
-      <c r="O8" s="14">
-        <v>-1.67</v>
+        <v>-16.899999999999999</v>
+      </c>
+      <c r="O8" s="15">
+        <v>2.72</v>
       </c>
       <c r="P8" s="13">
-        <v>18.309999999999999</v>
-      </c>
-      <c r="Q8" s="14">
-        <v>-3.98</v>
+        <v>20.7</v>
+      </c>
+      <c r="Q8" s="12">
+        <v>-3.25</v>
       </c>
     </row>
     <row r="9" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="5">
-        <v>45839</v>
+        <v>45870</v>
       </c>
       <c r="B9" s="6" t="s">
         <v>17</v>
@@ -1655,39 +1655,39 @@
         <v>17</v>
       </c>
       <c r="H9" s="8">
-        <v>2.75</v>
-      </c>
-      <c r="I9" s="15">
-        <v>4.99</v>
+        <v>2.88</v>
+      </c>
+      <c r="I9" s="14">
+        <v>4.8600000000000003</v>
       </c>
       <c r="J9" s="7">
-        <v>-6.01</v>
+        <v>-1.67</v>
       </c>
       <c r="K9" s="8">
-        <v>15.43</v>
+        <v>18.309999999999999</v>
       </c>
       <c r="L9" s="7">
-        <v>-4.4000000000000004</v>
+        <v>-3.98</v>
       </c>
       <c r="M9" s="8">
-        <v>2.75</v>
-      </c>
-      <c r="N9" s="15">
-        <v>4.99</v>
+        <v>2.88</v>
+      </c>
+      <c r="N9" s="14">
+        <v>4.8600000000000003</v>
       </c>
       <c r="O9" s="7">
-        <v>-6.01</v>
+        <v>-1.67</v>
       </c>
       <c r="P9" s="8">
-        <v>15.43</v>
+        <v>18.309999999999999</v>
       </c>
       <c r="Q9" s="7">
-        <v>-4.4000000000000004</v>
+        <v>-3.98</v>
       </c>
     </row>
     <row r="10" spans="1:17" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="10">
-        <v>45809</v>
+        <v>45839</v>
       </c>
       <c r="B10" s="11" t="s">
         <v>17</v>
@@ -1708,39 +1708,39 @@
         <v>17</v>
       </c>
       <c r="H10" s="13">
-        <v>2.62</v>
-      </c>
-      <c r="I10" s="12">
-        <v>6.62</v>
+        <v>2.75</v>
+      </c>
+      <c r="I10" s="15">
+        <v>4.99</v>
       </c>
       <c r="J10" s="12">
-        <v>7.24</v>
+        <v>-6.01</v>
       </c>
       <c r="K10" s="13">
-        <v>12.68</v>
-      </c>
-      <c r="L10" s="14">
-        <v>-4.04</v>
+        <v>15.43</v>
+      </c>
+      <c r="L10" s="12">
+        <v>-4.4000000000000004</v>
       </c>
       <c r="M10" s="13">
-        <v>2.62</v>
-      </c>
-      <c r="N10" s="12">
-        <v>6.62</v>
+        <v>2.75</v>
+      </c>
+      <c r="N10" s="15">
+        <v>4.99</v>
       </c>
       <c r="O10" s="12">
-        <v>7.24</v>
+        <v>-6.01</v>
       </c>
       <c r="P10" s="13">
-        <v>12.68</v>
-      </c>
-      <c r="Q10" s="14">
-        <v>-4.04</v>
+        <v>15.43</v>
+      </c>
+      <c r="Q10" s="12">
+        <v>-4.4000000000000004</v>
       </c>
     </row>
     <row r="11" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="5">
-        <v>45778</v>
+        <v>45809</v>
       </c>
       <c r="B11" s="6" t="s">
         <v>17</v>
@@ -1761,39 +1761,39 @@
         <v>17</v>
       </c>
       <c r="H11" s="8">
-        <v>2.4500000000000002</v>
-      </c>
-      <c r="I11" s="15">
-        <v>7.93</v>
-      </c>
-      <c r="J11" s="15">
-        <v>6.04</v>
+        <v>2.62</v>
+      </c>
+      <c r="I11" s="14">
+        <v>6.62</v>
+      </c>
+      <c r="J11" s="14">
+        <v>7.24</v>
       </c>
       <c r="K11" s="8">
-        <v>10.07</v>
+        <v>12.68</v>
       </c>
       <c r="L11" s="7">
-        <v>-6.6</v>
+        <v>-4.04</v>
       </c>
       <c r="M11" s="8">
-        <v>2.4500000000000002</v>
-      </c>
-      <c r="N11" s="15">
-        <v>7.93</v>
-      </c>
-      <c r="O11" s="15">
-        <v>6.04</v>
+        <v>2.62</v>
+      </c>
+      <c r="N11" s="14">
+        <v>6.62</v>
+      </c>
+      <c r="O11" s="14">
+        <v>7.24</v>
       </c>
       <c r="P11" s="8">
-        <v>10.07</v>
+        <v>12.68</v>
       </c>
       <c r="Q11" s="7">
-        <v>-6.6</v>
+        <v>-4.04</v>
       </c>
     </row>
     <row r="12" spans="1:17" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="10">
-        <v>45748</v>
+        <v>45778</v>
       </c>
       <c r="B12" s="11" t="s">
         <v>17</v>
@@ -1814,39 +1814,39 @@
         <v>17</v>
       </c>
       <c r="H12" s="13">
-        <v>2.27</v>
-      </c>
-      <c r="I12" s="12">
-        <v>20.8</v>
-      </c>
-      <c r="J12" s="14">
-        <v>-4.57</v>
+        <v>2.4500000000000002</v>
+      </c>
+      <c r="I12" s="15">
+        <v>7.93</v>
+      </c>
+      <c r="J12" s="15">
+        <v>6.04</v>
       </c>
       <c r="K12" s="13">
-        <v>7.61</v>
-      </c>
-      <c r="L12" s="14">
-        <v>-10.1</v>
+        <v>10.07</v>
+      </c>
+      <c r="L12" s="12">
+        <v>-6.6</v>
       </c>
       <c r="M12" s="13">
-        <v>2.27</v>
-      </c>
-      <c r="N12" s="12">
-        <v>20.8</v>
-      </c>
-      <c r="O12" s="14">
-        <v>-4.57</v>
+        <v>2.4500000000000002</v>
+      </c>
+      <c r="N12" s="15">
+        <v>7.93</v>
+      </c>
+      <c r="O12" s="15">
+        <v>6.04</v>
       </c>
       <c r="P12" s="13">
-        <v>7.61</v>
-      </c>
-      <c r="Q12" s="14">
-        <v>-10.1</v>
+        <v>10.07</v>
+      </c>
+      <c r="Q12" s="12">
+        <v>-6.6</v>
       </c>
     </row>
     <row r="13" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="5">
-        <v>45717</v>
+        <v>45748</v>
       </c>
       <c r="B13" s="6" t="s">
         <v>17</v>
@@ -1867,39 +1867,39 @@
         <v>17</v>
       </c>
       <c r="H13" s="8">
-        <v>1.88</v>
-      </c>
-      <c r="I13" s="15">
-        <v>19.5</v>
+        <v>2.27</v>
+      </c>
+      <c r="I13" s="14">
+        <v>20.8</v>
       </c>
       <c r="J13" s="7">
-        <v>-24.1</v>
+        <v>-4.57</v>
       </c>
       <c r="K13" s="8">
-        <v>5.34</v>
+        <v>7.61</v>
       </c>
       <c r="L13" s="7">
-        <v>-12.2</v>
+        <v>-10.1</v>
       </c>
       <c r="M13" s="8">
-        <v>1.88</v>
-      </c>
-      <c r="N13" s="15">
-        <v>19.5</v>
+        <v>2.27</v>
+      </c>
+      <c r="N13" s="14">
+        <v>20.8</v>
       </c>
       <c r="O13" s="7">
-        <v>-24.1</v>
+        <v>-4.57</v>
       </c>
       <c r="P13" s="8">
-        <v>5.34</v>
+        <v>7.61</v>
       </c>
       <c r="Q13" s="7">
-        <v>-12.2</v>
+        <v>-10.1</v>
       </c>
     </row>
     <row r="14" spans="1:17" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="10">
-        <v>45689</v>
+        <v>45717</v>
       </c>
       <c r="B14" s="11" t="s">
         <v>17</v>
@@ -1920,39 +1920,39 @@
         <v>17</v>
       </c>
       <c r="H14" s="13">
-        <v>1.57</v>
-      </c>
-      <c r="I14" s="14">
-        <v>-16.5</v>
-      </c>
-      <c r="J14" s="14">
-        <v>-9.35</v>
+        <v>1.88</v>
+      </c>
+      <c r="I14" s="15">
+        <v>19.5</v>
+      </c>
+      <c r="J14" s="12">
+        <v>-24.1</v>
       </c>
       <c r="K14" s="13">
-        <v>3.46</v>
-      </c>
-      <c r="L14" s="14">
-        <v>-4.07</v>
+        <v>5.34</v>
+      </c>
+      <c r="L14" s="12">
+        <v>-12.2</v>
       </c>
       <c r="M14" s="13">
-        <v>1.57</v>
-      </c>
-      <c r="N14" s="14">
-        <v>-16.5</v>
-      </c>
-      <c r="O14" s="14">
-        <v>-9.35</v>
+        <v>1.88</v>
+      </c>
+      <c r="N14" s="15">
+        <v>19.5</v>
+      </c>
+      <c r="O14" s="12">
+        <v>-24.1</v>
       </c>
       <c r="P14" s="13">
-        <v>3.46</v>
-      </c>
-      <c r="Q14" s="14">
-        <v>-4.07</v>
+        <v>5.34</v>
+      </c>
+      <c r="Q14" s="12">
+        <v>-12.2</v>
       </c>
     </row>
     <row r="15" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="5">
-        <v>45658</v>
+        <v>45689</v>
       </c>
       <c r="B15" s="6" t="s">
         <v>17</v>
@@ -1973,39 +1973,39 @@
         <v>17</v>
       </c>
       <c r="H15" s="8">
-        <v>1.89</v>
-      </c>
-      <c r="I15" s="15">
-        <v>17.5</v>
-      </c>
-      <c r="J15" s="15">
-        <v>0.84</v>
+        <v>1.57</v>
+      </c>
+      <c r="I15" s="7">
+        <v>-16.5</v>
+      </c>
+      <c r="J15" s="7">
+        <v>-9.35</v>
       </c>
       <c r="K15" s="8">
-        <v>1.89</v>
-      </c>
-      <c r="L15" s="15">
-        <v>0.84</v>
+        <v>3.46</v>
+      </c>
+      <c r="L15" s="7">
+        <v>-4.07</v>
       </c>
       <c r="M15" s="8">
-        <v>1.89</v>
-      </c>
-      <c r="N15" s="15">
-        <v>17.5</v>
-      </c>
-      <c r="O15" s="15">
-        <v>0.84</v>
+        <v>1.57</v>
+      </c>
+      <c r="N15" s="7">
+        <v>-16.5</v>
+      </c>
+      <c r="O15" s="7">
+        <v>-9.35</v>
       </c>
       <c r="P15" s="8">
-        <v>1.89</v>
-      </c>
-      <c r="Q15" s="15">
-        <v>0.84</v>
+        <v>3.46</v>
+      </c>
+      <c r="Q15" s="7">
+        <v>-4.07</v>
       </c>
     </row>
     <row r="16" spans="1:17" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="10">
-        <v>45627</v>
+        <v>45658</v>
       </c>
       <c r="B16" s="11" t="s">
         <v>17</v>
@@ -2026,86 +2026,139 @@
         <v>17</v>
       </c>
       <c r="H16" s="13">
-        <v>1.61</v>
-      </c>
-      <c r="I16" s="14">
-        <v>-9.26</v>
-      </c>
-      <c r="J16" s="14">
-        <v>-23.8</v>
+        <v>1.89</v>
+      </c>
+      <c r="I16" s="15">
+        <v>17.5</v>
+      </c>
+      <c r="J16" s="15">
+        <v>0.84</v>
       </c>
       <c r="K16" s="13">
-        <v>26.68</v>
-      </c>
-      <c r="L16" s="14">
-        <v>-12</v>
+        <v>1.89</v>
+      </c>
+      <c r="L16" s="15">
+        <v>0.84</v>
       </c>
       <c r="M16" s="13">
-        <v>1.61</v>
-      </c>
-      <c r="N16" s="14">
-        <v>-9.26</v>
-      </c>
-      <c r="O16" s="14">
-        <v>-23.8</v>
+        <v>1.89</v>
+      </c>
+      <c r="N16" s="15">
+        <v>17.5</v>
+      </c>
+      <c r="O16" s="15">
+        <v>0.84</v>
       </c>
       <c r="P16" s="13">
-        <v>26.68</v>
-      </c>
-      <c r="Q16" s="14">
-        <v>-12</v>
+        <v>1.89</v>
+      </c>
+      <c r="Q16" s="15">
+        <v>0.84</v>
       </c>
     </row>
     <row r="17" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="5">
+        <v>45627</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C17" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D17" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="E17" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="F17" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="G17" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="H17" s="8">
+        <v>1.61</v>
+      </c>
+      <c r="I17" s="7">
+        <v>-9.26</v>
+      </c>
+      <c r="J17" s="7">
+        <v>-23.8</v>
+      </c>
+      <c r="K17" s="8">
+        <v>26.68</v>
+      </c>
+      <c r="L17" s="7">
+        <v>-12</v>
+      </c>
+      <c r="M17" s="8">
+        <v>1.61</v>
+      </c>
+      <c r="N17" s="7">
+        <v>-9.26</v>
+      </c>
+      <c r="O17" s="7">
+        <v>-23.8</v>
+      </c>
+      <c r="P17" s="8">
+        <v>26.68</v>
+      </c>
+      <c r="Q17" s="7">
+        <v>-12</v>
+      </c>
+    </row>
+    <row r="18" spans="1:17" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="10">
         <v>45597</v>
       </c>
-      <c r="B17" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="C17" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="D17" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="E17" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="F17" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="G17" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="H17" s="8">
+      <c r="B18" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="C18" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="D18" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E18" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="F18" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="G18" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="H18" s="13">
         <v>1.77</v>
       </c>
-      <c r="I17" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="J17" s="7">
+      <c r="I18" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="J18" s="12">
         <v>-15.2</v>
       </c>
-      <c r="K17" s="8">
+      <c r="K18" s="13">
         <v>25.08</v>
       </c>
-      <c r="L17" s="7">
+      <c r="L18" s="12">
         <v>-11.1</v>
       </c>
-      <c r="M17" s="8">
+      <c r="M18" s="13">
         <v>1.77</v>
       </c>
-      <c r="N17" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="O17" s="7">
+      <c r="N18" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="O18" s="12">
         <v>-15.2</v>
       </c>
-      <c r="P17" s="8">
+      <c r="P18" s="13">
         <v>25.08</v>
       </c>
-      <c r="Q17" s="7">
+      <c r="Q18" s="12">
         <v>-11.1</v>
       </c>
     </row>
